--- a/public/datos/plan_cuadrillas_por_municipio.xlsx
+++ b/public/datos/plan_cuadrillas_por_municipio.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AC$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Plan'!$A$1:$AD$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,90 +510,95 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale de</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Duerme en</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tramo de llegada (min)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tramo de salida (min)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Carretera del día (min)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Km del día</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Concepto (tablero del Valle)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado (MEN)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Nivel de afectación (MEN)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Tipo de vía</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Vía de acceso</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Coordenada en revisión</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Latitud</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Longitud</t>
         </is>
@@ -651,80 +656,85 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>VEREDA LA CLORINDA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>56.69</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>63.34</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>120</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>51.2</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>3.54959</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>-76.632525</v>
       </c>
     </row>
@@ -780,80 +790,85 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>BORRERO AYERBE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>62.64</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>67.12</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>129.8</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>62.1</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>LA JULIA CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>3.574795</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>-76.64960499999999</v>
       </c>
     </row>
@@ -909,80 +924,85 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL CARMEN</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>64.3</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>69.73</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>134</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>63.1</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>EL CARMEN - VIA SIMON BOLIVAR CRUCE VIA 3201</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>3.5527246</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>-76.6515909</v>
       </c>
     </row>
@@ -1038,75 +1058,80 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>CORREG EL PALMAR</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>62.7</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>65.98999999999999</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>128.7</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 9 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>3.6041469</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-76.6490644</v>
       </c>
     </row>
@@ -1162,75 +1187,80 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>VEREDA JIGUALES</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>82.3</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>76.19</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>158.5</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.595044</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-76.665947</v>
       </c>
     </row>
@@ -1246,11 +1276,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1286,75 +1316,80 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL LIMONAR</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>121.24</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>103.59</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>224.8</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>110.3</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.606151</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>-76.70789000000001</v>
       </c>
     </row>
@@ -1374,7 +1409,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1410,80 +1445,85 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>KR 3 2 000</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>76.88</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>85.62</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>162.5</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>71.2</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Carrera 2</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>3.6489149</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-76.56672399999999</v>
       </c>
     </row>
@@ -1503,7 +1543,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1539,80 +1579,85 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>KR 1 3 14</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>76.91</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>85.34999999999999</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>162.3</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 49 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Diagonal 1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>3.6478665</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-76.56629270000001</v>
       </c>
     </row>
@@ -1632,7 +1677,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1668,80 +1713,85 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO SANTA MARIA</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>103</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>101.04</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>204</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>121.1</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 7 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>SANTA MARIA - EL LIMONAR CRUCE VIA 23319VL02 K5+555</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>3.63352</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-76.715591</v>
       </c>
     </row>
@@ -1761,7 +1811,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1797,80 +1847,85 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>KR 6 6 67</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0.73</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>3.1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.8</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Carrera 6</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>3.85991597259148</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-76.38388046730552</v>
       </c>
     </row>
@@ -1890,7 +1945,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1926,80 +1981,85 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>KR 5 5 79</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>0.37</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>3.1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.8</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>3.86056963997</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-76.38430955440001</v>
       </c>
     </row>
@@ -2015,11 +2075,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2055,80 +2115,85 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>VEREDA SAN JUAN</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>59.23</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>63.8</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>123</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>46.8</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>MEDIACANOA - MIRAVALLE - CAMPO ALEGRE - CRUCE VIA 2302</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>3.962278</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>-76.40526699999999</v>
       </c>
     </row>
@@ -2144,11 +2209,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2184,80 +2249,85 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO  MEDIA CANOA</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>9.4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>40.8</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>62.9</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 24 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>MEDIACANOA - PRIMAVERA</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.900556391368746</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>-76.37662112784321</v>
       </c>
     </row>
@@ -2273,11 +2343,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2313,80 +2383,85 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>KR 9 13 08</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>40.8</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>43.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>62.9</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Carrera 9</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>3.82299113556</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>-76.52146344489999</v>
       </c>
     </row>
@@ -2406,7 +2481,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2442,75 +2517,80 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO VILLAMARIA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>40.51</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>15.26</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>85.2</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>62.8</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>3.716456</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>-76.47793299999999</v>
       </c>
     </row>
@@ -2530,7 +2610,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2566,80 +2646,85 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>KR 4 5 34</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>15.26</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>29.46</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>85.2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>62.8</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Carrera 4</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>3.699871998710244</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>-76.44279828333418</v>
       </c>
     </row>
@@ -2659,7 +2744,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2695,80 +2780,85 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>VEREDA CAIMITAL</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>59.58</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>63.82</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>123.4</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>81.2</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 32 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>EL TAMBOR - LA RIVERA - OCACHE</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>3.741864</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>-76.49940700000001</v>
       </c>
     </row>
@@ -2788,7 +2878,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2824,80 +2914,85 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>CORREG LA MARIA</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Yotoco</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>140.39</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>102.33</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>242.7</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>126.3</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>LA GUAIRA - KM113- LOMITAS</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>3.6919524</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>-76.63414659999999</v>
       </c>
     </row>
@@ -2953,70 +3048,75 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>PANORAMA PARTE ALTA</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>28.88</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>45.9</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 0 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Calle 8</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.563871751</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>-76.49699</v>
       </c>
     </row>
@@ -3072,70 +3172,75 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>KR 18 G 17 A 60</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2.7</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>40</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>45.9</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.569142</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>-76.49818</v>
       </c>
     </row>
@@ -3191,70 +3296,75 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>CR 28 NO 33 12</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>1.17</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>2.6</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>0.8</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Calle 34</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>3.530963312</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>-76.29813</v>
       </c>
     </row>
@@ -3310,70 +3420,75 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>CLL 37 NO 42A 110</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>6.63</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>5.5</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>14.7</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>4.8</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Calle 38</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>3.534745489</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>-76.31374</v>
       </c>
     </row>
@@ -3429,70 +3544,75 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>CLL 34 NO 31 71</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>5.5</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>2.57</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>14.7</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>4.8</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Calle 34</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>3.531528575</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>-76.30112</v>
       </c>
     </row>
@@ -3548,70 +3668,75 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>CL 40 KR 12 ESQ</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>5.49</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>4.7</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>12</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Calle 40</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>3.535564379</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>-76.28555</v>
       </c>
     </row>
@@ -3667,70 +3792,75 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>CR 22 CLL  33 ESQ</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>4.7</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>12</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>4</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Calle 33</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>3.529666412</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>-76.29319</v>
       </c>
     </row>
@@ -3786,70 +3916,75 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>KR 25 21 52</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>4.81</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>0.26</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>10.2</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>3.2</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Calle 21</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>3.519487</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>-76.29709</v>
       </c>
     </row>
@@ -3905,65 +4040,70 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>KR 24 A 20 97</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>0.26</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>5.15</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>10.2</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>3.2</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 27 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>3.518847963</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>-76.29706</v>
       </c>
     </row>
@@ -3979,11 +4119,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4019,65 +4159,70 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>KR 16 32 02</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>7.29</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>0.73</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>14.3</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>4</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>3.528177503</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>-76.28814</v>
       </c>
     </row>
@@ -4093,11 +4238,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4133,65 +4278,70 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>CLL 31NO 15 44</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>0.73</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>6.24</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>14.3</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>4</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>3.52714115</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>-76.28801</v>
       </c>
     </row>
@@ -4211,7 +4361,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4247,70 +4397,75 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>CLL 2ENO 31 20</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3.67</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>3.91</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>14.4</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>4.8</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 17 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Calle 32A</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>3.528611111</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>-76.28861000000001</v>
       </c>
     </row>
@@ -4330,7 +4485,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4366,70 +4521,75 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>CLL 30 NO 7  40</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>3.91</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>6.85</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>14.4</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>4.8</v>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Calle 30</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>3.523726631</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>-76.28198</v>
       </c>
     </row>
@@ -4449,7 +4609,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4485,70 +4645,75 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>KR 31 15 A 40</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>6.96</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>4.04</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>14</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>4.5</v>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Carrera 30</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>3.514837633</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>-76.30277</v>
       </c>
     </row>
@@ -4568,7 +4733,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4604,70 +4769,75 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>CR 27 NO  25 50</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>4.04</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>3.03</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>14</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>4.5</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Carrera 27</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>3.522721634</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>-76.29872</v>
       </c>
     </row>
@@ -4687,7 +4857,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4723,70 +4893,75 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>CR 35 NO 25B 10</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>6.08</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>14.5</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>4.7</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 31 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Carrera 35</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>3.523493621</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>-76.306</v>
       </c>
     </row>
@@ -4806,7 +4981,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4842,70 +5017,75 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>CL 23 33 A 37</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>2.62</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>5.81</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>14.5</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>4.7</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Calle 23</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>3.521595</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>-76.30551</v>
       </c>
     </row>
@@ -4925,7 +5105,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4961,65 +5141,70 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>CORREG AMAIME</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>18.8</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>14.44</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>43.1</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>22.4</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 58 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>3.608742554</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>-76.26954000000001</v>
       </c>
     </row>
@@ -5039,7 +5224,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5075,70 +5260,75 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>IND KR 35 CL 60 EQ</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>14.44</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>43.1</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>22.4</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 8 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Carrera 35</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>3.5498</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>-76.306017</v>
       </c>
     </row>
@@ -5154,11 +5344,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5194,65 +5384,70 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>VDA LA PAMPA</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>20.23</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>5.77</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>44.6</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>23.1</v>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 60 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>3.593751949</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>-76.25812000000001</v>
       </c>
     </row>
@@ -5268,11 +5463,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5308,65 +5503,70 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>CORREG AMAIME</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5.77</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>18.61</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>44.6</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>23.1</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>En evaluación</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Sin afectación</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 134 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>3.606101352</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>-76.26662</v>
       </c>
     </row>
@@ -5382,11 +5582,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5422,70 +5622,75 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>KR 26 CL 12 ESQ</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>6.98</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>4.37</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>34.9</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>17.8</v>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Calle 12</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>3.51096553</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>-76.29906</v>
       </c>
     </row>
@@ -5501,11 +5706,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5541,70 +5746,75 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t xml:space="preserve">IND CL 5 29 107 </t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Palmira</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>4.37</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>23.51</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>34.9</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>17.8</v>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>3.502527</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>-76.30364</v>
       </c>
     </row>
@@ -5624,7 +5834,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5660,80 +5870,85 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>CL 7 9 11</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>0.23</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>2.2</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>0.6</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 2 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>3.407489</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>-76.34917799999999</v>
       </c>
     </row>
@@ -5753,7 +5968,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5789,80 +6004,85 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>CL 7 8 42</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>0.25</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>2.2</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>0.6</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>Calle 7</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>3.40761667</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>-76.34858894</v>
       </c>
     </row>
@@ -5882,7 +6102,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5918,70 +6138,75 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>CR 21 NO 9-89</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>27.65</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>28.95</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>44</v>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 23 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>3.32644406118</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AD45" t="n">
         <v>-76.23742270629999</v>
       </c>
     </row>
@@ -6001,7 +6226,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -6037,80 +6262,85 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>CR 12 NO 10-81</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>28.95</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>44</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>Afectación menor</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 1 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>CALLEJON FLORO MERCADO CRUCE VIA 13025VL04-2E</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>3.39537597879</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
         <v>-76.3859481842</v>
       </c>
     </row>
@@ -6130,7 +6360,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -6166,65 +6396,70 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
           <t>CLL 20 NO 13A-16</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>47.14</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>17.94</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>59.3</v>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>3.573823</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
         <v>-76.48081000000001</v>
       </c>
     </row>
@@ -6244,7 +6479,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6280,70 +6515,75 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
           <t>CLL 10 NO 31A-150</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Candelaria</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Cali</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>17.94</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>23.81</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>59.3</v>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 22 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>Calle 10</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>3.51115</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>-76.51866</v>
       </c>
     </row>
@@ -6399,80 +6639,85 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>CORREG EL VILLAR</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>138.32</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>236</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>113.2</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 34 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>LA PLAYA CRUCE CON VIA 04123VL13-5G3 EN K3</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>4.819842722212309</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>-76.08934449628445</v>
       </c>
     </row>
@@ -6528,80 +6773,85 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>CORREG EL VERGEL</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>65.8</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>65.38</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>131.2</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>54.1</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 13 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>EL VERGEL CRUCE CON VIA 04123VL13-5C EN K6+384</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>4.86111676163</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>-75.99733304110001</v>
       </c>
     </row>
@@ -6657,80 +6907,85 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
           <t>VEREDA EL PLACER</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>104.08</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>102.25</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>206.3</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>85.8</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>EL REAL PLACER CRUCE CON VIA 0414802VL-G EN K22+316</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>4.7883859</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>-76.0724936</v>
       </c>
     </row>
@@ -6786,80 +7041,85 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
           <t>VEREDA LA ESTRELLA</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>75.41</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>150.8</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>76.5</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>LAS BRISAS - EL BRILLANTE</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>4.72634</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>-76.11562499999999</v>
       </c>
     </row>
@@ -6915,80 +7175,85 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
           <t>CORRG SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>40.95</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>15.49</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>103.2</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>SAN FRANCISCO CRUCE 82323VL02-N K0+000</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>4.68415925</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>-76.0351458</v>
       </c>
     </row>
@@ -7044,80 +7309,85 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t>CLL 18 NO 1-100</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Cartago</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>15.49</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>46.69</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>103.2</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 41 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>Calle 18</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>4.60769678</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>-76.07215911999999</v>
       </c>
     </row>
@@ -7133,11 +7403,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7173,65 +7443,70 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
           <t>CORREGIMENTO LA FLORIDA</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>33.24</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>34.3</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>67.5</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>36.4</v>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>4.64998614</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>-76.13698533</v>
       </c>
     </row>
@@ -7251,7 +7526,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -7287,80 +7562,85 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
           <t>CRA 14 NO 13-25</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>36.24</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>0.17</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R56" t="n">
+      <c r="S56" t="n">
         <v>44.3</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB56" t="n">
+      <c r="AC56" t="n">
         <v>4.5307229</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AD56" t="n">
         <v>-76.1031742</v>
       </c>
     </row>
@@ -7380,7 +7660,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -7416,80 +7696,85 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>CL 13 14 51</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>0.17</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>39.7</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>44.3</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>Calle 13</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB57" t="n">
+      <c r="AC57" t="n">
         <v>4.5306222</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
         <v>-76.10365280000001</v>
       </c>
     </row>
@@ -7509,7 +7794,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7545,80 +7830,85 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
           <t>CL 16 16 00</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>35.88</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>13.08</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>104.5</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 11 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>Calle 16</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB58" t="n">
+      <c r="AC58" t="n">
         <v>4.53325</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AD58" t="n">
         <v>-76.1032</v>
       </c>
     </row>
@@ -7638,7 +7928,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7674,80 +7964,85 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>CL 8 7 61</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Versalles</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>13.08</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>55.52</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>104.5</v>
       </c>
-      <c r="R59" t="n">
+      <c r="S59" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 6 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>Carrera 8</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB59" t="n">
+      <c r="AC59" t="n">
         <v>4.522653896403604</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
         <v>-76.0369985666723</v>
       </c>
     </row>
@@ -7767,7 +8062,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -7803,70 +8098,75 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
           <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>7.41</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>42.09</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>100.2</v>
       </c>
-      <c r="R60" t="n">
+      <c r="S60" t="n">
         <v>57</v>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>via principal pavimentada</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>Calle 27</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB60" t="n">
+      <c r="AC60" t="n">
         <v>4.088515899</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AD60" t="n">
         <v>-76.22009</v>
       </c>
     </row>
@@ -7886,7 +8186,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -7922,80 +8222,85 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>CORREG SALONICA</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>42.09</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>50.65</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>100.2</v>
       </c>
-      <c r="R61" t="n">
+      <c r="S61" t="n">
         <v>57</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>en revisión de la mesa</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB61" t="n">
+      <c r="AC61" t="n">
         <v>4.1258314</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AD61" t="n">
         <v>-76.3722336</v>
       </c>
     </row>
@@ -8015,7 +8320,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -8051,65 +8356,70 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
           <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>32.44</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="R62" t="n">
+      <c r="S62" t="n">
         <v>59</v>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>camino destapado</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB62" t="n">
+      <c r="AC62" t="n">
         <v>4.090555556</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AD62" t="n">
         <v>-76.22221999999999</v>
       </c>
     </row>
@@ -8129,7 +8439,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -8165,80 +8475,85 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
           <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>32.44</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>41.58</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="R63" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="R63" t="n">
+      <c r="S63" t="n">
         <v>59</v>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>camino rural sin categoria</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>difícil</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB63" t="n">
+      <c r="AC63" t="n">
         <v>4.0553</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AD63" t="n">
         <v>-76.35465000000001</v>
       </c>
     </row>
@@ -8254,11 +8569,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -8294,80 +8609,85 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>KR 18 15 40</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>46.98</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>0.67</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="R64" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R64" t="n">
+      <c r="S64" t="n">
         <v>48.5</v>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>No habitable</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB64" t="n">
+      <c r="AC64" t="n">
         <v>4.208406</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AD64" t="n">
         <v>-76.31959500000001</v>
       </c>
     </row>
@@ -8383,11 +8703,11 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -8423,70 +8743,75 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
           <t>KR 18 15 27</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>0.67</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>44.3</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
         <v>48.5</v>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Carrera 18</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB65" t="n">
+      <c r="AC65" t="n">
         <v>4.210077</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AD65" t="n">
         <v>-76.319047</v>
       </c>
     </row>
@@ -8502,11 +8827,11 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>martes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -8542,80 +8867,85 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
           <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>77.20999999999999</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>69.08</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="R66" t="n">
         <v>146.3</v>
       </c>
-      <c r="R66" t="n">
+      <c r="S66" t="n">
         <v>74.2</v>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB66" t="n">
+      <c r="AC66" t="n">
         <v>4.210564</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AD66" t="n">
         <v>-76.38158300000001</v>
       </c>
     </row>
@@ -8635,7 +8965,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -8671,80 +9001,85 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
           <t>KR 2 2 66</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>57.35</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>14.61</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="R67" t="n">
         <v>115.4</v>
       </c>
-      <c r="R67" t="n">
+      <c r="S67" t="n">
         <v>93.2</v>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 43 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>BOLIVAR CRUCE CON VIA DE INVIAS 2302 EN TRAMO 23020 INICIO A 52m DE INICIO DE VIA 10023VL02B</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB67" t="n">
+      <c r="AC67" t="n">
         <v>4.340805</v>
       </c>
-      <c r="AC67" t="n">
+      <c r="AD67" t="n">
         <v>-76.17979800000001</v>
       </c>
     </row>
@@ -8764,7 +9099,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -8800,80 +9135,85 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
           <t>CL 4 5 38</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="O68" t="n">
+      <c r="P68" t="n">
         <v>14.61</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>43.44</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>115.4</v>
       </c>
-      <c r="R68" t="n">
+      <c r="S68" t="n">
         <v>93.2</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>Afectación parcial</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Moderado</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 10 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>Carrera 5</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB68" t="n">
+      <c r="AC68" t="n">
         <v>4.412260842287796</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AD68" t="n">
         <v>-76.15737540436542</v>
       </c>
     </row>
@@ -8893,7 +9233,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -8929,80 +9269,85 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
           <t>CL 6 4 15</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
         <v>3.3</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>32.49</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="R69" t="n">
+      <c r="S69" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>Uso restringido</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>Calle 6</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB69" t="n">
+      <c r="AC69" t="n">
         <v>4.165067</v>
       </c>
-      <c r="AC69" t="n">
+      <c r="AD69" t="n">
         <v>-76.16943499999999</v>
       </c>
     </row>
@@ -9022,7 +9367,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>martes</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -9058,80 +9403,85 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
           <t>CL 10 KR 10 EQ</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Andalucia</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="O70" t="n">
+      <c r="P70" t="n">
         <v>32.49</v>
       </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
         <v>58.56</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="R70" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="R70" t="n">
+      <c r="S70" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>Riesgo inminente de colapso</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>via terciaria</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 18 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>Carrera 10</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB70" t="n">
+      <c r="AC70" t="n">
         <v>4.3959229</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AD70" t="n">
         <v>-76.0708454</v>
       </c>
     </row>
@@ -9151,7 +9501,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>miércoles</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -9187,85 +9537,90 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>CL 5 11 15</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Caicedonia</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Pereira</t>
         </is>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>1.47</v>
       </c>
-      <c r="P71" t="n">
+      <c r="Q71" t="n">
         <v>112.59</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>114.1</v>
       </c>
-      <c r="R71" t="n">
+      <c r="S71" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>Peligro de colapso</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>aprobado por la mesa</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>Colapso parcial</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>Critico</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>calle de casco urbano</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>fácil</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>Calle 5</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AB71" t="n">
+      <c r="AC71" t="n">
         <v>4.329633623</v>
       </c>
-      <c r="AC71" t="n">
+      <c r="AD71" t="n">
         <v>-75.82531724</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC71"/>
+  <autoFilter ref="A1:AD71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9276,7 +9631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9291,7 +9646,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>+ Palmira, Yumbo y Tuluá. Las 43 del BID más las que aportan tres secretarías certificadas. Es el alcance recomendado: el más grande que cabe en el TdR sin cambiarle nada. Sin volver a la base los fines de semana.</t>
+          <t>+ Palmira, Yumbo y Tuluá. Las 43 del BID más las que aportan tres secretarías certificadas. Es el alcance recomendado: el más grande que cabe en el TdR sin cambiarle nada. Sin volver a la base los domingos.</t>
         </is>
       </c>
     </row>
@@ -9303,154 +9658,180 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Jornada</t>
+          <t>Semana de campo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
+          <t>De lunes a sábado, seis días. La semana 1 son los días 1 a 6, la 2 del 7 al 12, y así.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tiempos</t>
+          <t>Jornada</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
+          <t>Hasta 8 horas contando carretera e inspecciones; cada inspección dura 3 horas.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Noches fuera</t>
+          <t>Tiempos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Una por cada día que la cuadrilla termina fuera de su base. Los fines de semana no se suman.</t>
+          <t>Mapbox, saliendo a las 7:00, entre sedes a las 11:00 y regresando a las 16:00 de un martes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Una por cada día que la cuadrilla termina fuera de su base. El domingo de descanso no se suma acá; para el alojamiento que se paga están las noches de hotel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>Coordenadas</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Las marcadas en revisión son provisionales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Cuadrilla</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Sedes</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Horas de carretera</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Km</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Noches fuera</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>15</v>
-      </c>
-      <c r="C9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1070</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Cuadrilla</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Días</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Sedes</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Horas de carretera</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Km</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Noches fuera</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Noches de hotel</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>7.5</v>
+        <v>34.9</v>
       </c>
       <c r="E10" t="n">
-        <v>244</v>
+        <v>1070</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>30.4</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1063</v>
+        <v>244</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public/datos/plan_cuadrillas_por_municipio.xlsx
+++ b/public/datos/plan_cuadrillas_por_municipio.xlsx
@@ -3452,7 +3452,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>En evaluación</t>
+          <t>Sin afectación</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_por_municipio.xlsx
+++ b/public/datos/plan_cuadrillas_por_municipio.xlsx
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/public/datos/plan_cuadrillas_por_municipio.xlsx
+++ b/public/datos/plan_cuadrillas_por_municipio.xlsx
@@ -3090,7 +3090,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 0 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 4 m de esa vía.</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Calle 8</t>
+          <t>Calle 7B</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3214,22 +3214,17 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 17 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Calle 7</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 3 m de esa vía.</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3279,11 +3274,6 @@
           <t>LA MILAGROSA</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA LA MILAGROSA</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>176520002279</t>
@@ -3292,16 +3282,6 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>CR 28 NO 33 12</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3325,36 +3305,6 @@
       </c>
       <c r="S22" t="n">
         <v>0.8</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 21 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Calle 34</t>
-        </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -3403,11 +3353,6 @@
           <t>TULIO RAFFO</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA JORGE ELIECER GAITAN</t>
-        </is>
-      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>176520001949</t>
@@ -3416,16 +3361,6 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>CLL 37 NO 42A 110</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3449,36 +3384,6 @@
       </c>
       <c r="S23" t="n">
         <v>4.8</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Calle 38</t>
-        </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
@@ -3527,11 +3432,6 @@
           <t>GREGORIO HERNANDEZ</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA LA MILAGROSA</t>
-        </is>
-      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>176520001825</t>
@@ -3540,16 +3440,6 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>CLL 34 NO 31 71</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3573,36 +3463,6 @@
       </c>
       <c r="S24" t="n">
         <v>4.8</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Calle 34</t>
-        </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -3651,11 +3511,6 @@
           <t>ALFONSO CABAL MADRIÑAN</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MERCEDES ABREGO</t>
-        </is>
-      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>176520001761</t>
@@ -3664,16 +3519,6 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>CL 40 KR 12 ESQ</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3697,36 +3542,6 @@
       </c>
       <c r="S25" t="n">
         <v>4</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Moderado</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Calle 40</t>
-        </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -3775,11 +3590,6 @@
           <t>JOSE MARIA CORDOBA</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA LA MILAGROSA</t>
-        </is>
-      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>176520001736</t>
@@ -3788,16 +3598,6 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>CR 22 CLL  33 ESQ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3821,36 +3621,6 @@
       </c>
       <c r="S26" t="n">
         <v>4</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 12 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Calle 33</t>
-        </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -4023,11 +3793,6 @@
           <t>SANTA TERESITA (U)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
-        </is>
-      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>176520001990</t>
@@ -4036,16 +3801,6 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>KR 24 A 20 97</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4069,31 +3824,6 @@
       </c>
       <c r="S28" t="n">
         <v>3.2</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Afectación parcial</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Moderado</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 27 m de esa vía.</t>
-        </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -4261,11 +3991,6 @@
           <t>SANTISIMA TRINIDAD</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
-        </is>
-      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>176520002317</t>
@@ -4274,16 +3999,6 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>CLL 31NO 15 44</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4307,31 +4022,6 @@
       </c>
       <c r="S30" t="n">
         <v>4</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 41 m de esa vía.</t>
-        </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -4380,11 +4070,6 @@
           <t>PRAXEDES ESPINOSA</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
-        </is>
-      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>176520002201</t>
@@ -4393,16 +4078,6 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>CLL 2ENO 31 20</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4426,36 +4101,6 @@
       </c>
       <c r="S31" t="n">
         <v>4.8</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 17 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Calle 32A</t>
-        </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -4504,11 +4149,6 @@
           <t>AGUSTIN CODAZZI</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA ALFONSO LOPEZ PUMAREJO</t>
-        </is>
-      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>176520001795</t>
@@ -4517,16 +4157,6 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>CLL 30 NO 7  40</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4550,36 +4180,6 @@
       </c>
       <c r="S32" t="n">
         <v>4.8</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 15 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Calle 30</t>
-        </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -4628,11 +4228,6 @@
           <t>MARIA ANTONIA PENAGOS</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MARIA ANTONIA PENAGOS</t>
-        </is>
-      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>176520002520</t>
@@ -4641,16 +4236,6 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>KR 31 15 A 40</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4674,36 +4259,6 @@
       </c>
       <c r="S33" t="n">
         <v>4.5</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 14 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Carrera 30</t>
-        </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -4752,11 +4307,6 @@
           <t>FRANCISCO DE PAULA SANTANDER</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MARIA ANTONIA PENAGOS</t>
-        </is>
-      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>176520001817</t>
@@ -4765,16 +4315,6 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>CR 27 NO  25 50</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4798,36 +4338,6 @@
       </c>
       <c r="S34" t="n">
         <v>4.5</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Carrera 27</t>
-        </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -4876,11 +4386,6 @@
           <t>MONSEÑOR GUILLERMO BECERRA</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA DOMINGO IRURITA</t>
-        </is>
-      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>176520001884</t>
@@ -4889,16 +4394,6 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>CR 35 NO 25B 10</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4922,36 +4417,6 @@
       </c>
       <c r="S35" t="n">
         <v>4.7</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 31 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Carrera 35</t>
-        </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -5059,22 +4524,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 16 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 35 m de esa vía.</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Calle 23</t>
+          <t>Carrera 33A</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5124,11 +4589,6 @@
           <t>VASCO NUÑEZ DE BALBOA</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA SEMILLA DE LA ESPERANZA</t>
-        </is>
-      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>276520000823</t>
@@ -5137,16 +4597,6 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>CORREG AMAIME</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5170,31 +4620,6 @@
       </c>
       <c r="S37" t="n">
         <v>22.4</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «service»). La sede queda a 58 m de esa vía.</t>
-        </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -5243,11 +4668,6 @@
           <t>BOSQUES DEL EDEN</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA ANTONIO LIZARAZO</t>
-        </is>
-      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>176520800167</t>
@@ -5256,16 +4676,6 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>IND KR 35 CL 60 EQ</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5289,36 +4699,6 @@
       </c>
       <c r="S38" t="n">
         <v>22.4</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>via terciaria</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 8 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Carrera 35</t>
-        </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -5367,11 +4747,6 @@
           <t>HELIODORO VILLEGAS</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA SEMILLA DE LA ESPERANZA</t>
-        </is>
-      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>276520002010</t>
@@ -5380,16 +4755,6 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>VDA LA PAMPA</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5413,31 +4778,6 @@
       </c>
       <c r="S39" t="n">
         <v>23.1</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>camino rural sin categoria</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 60 m de esa vía.</t>
-        </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -5486,11 +4826,6 @@
           <t>SEMILLA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA SEMILLA DE LA ESPERANZA</t>
-        </is>
-      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>276520005248</t>
@@ -5499,16 +4834,6 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>CORREG AMAIME</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5532,31 +4857,6 @@
       </c>
       <c r="S40" t="n">
         <v>23.1</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Sin afectación</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>via principal pavimentada</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 134 m de esa vía.</t>
-        </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -5605,11 +4905,6 @@
           <t>SUSANA LOPEZ DE VALENCIA</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MARIA ANTONIA PENAGOS</t>
-        </is>
-      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>176520002694</t>
@@ -5618,16 +4913,6 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>Palmira</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>KR 26 CL 12 ESQ</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5651,36 +4936,6 @@
       </c>
       <c r="S41" t="n">
         <v>17.8</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 20 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Calle 12</t>
-        </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -5729,11 +4984,6 @@
           <t>MEGACOLEGIO DEL SUR</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>INSTITUCION EDUCATIVA MARIA ANTONIA PENAGOS</t>
-        </is>
-      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>176520800222</t>
@@ -5742,16 +4992,6 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>PALMIRA</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IND CL 5 29 107 </t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5775,36 +5015,6 @@
       </c>
       <c r="S42" t="n">
         <v>17.8</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Afectación menor</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>calle de casco urbano</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Calle 5</t>
-        </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -7845,7 +7055,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -7855,10 +7065,10 @@
         <v>13.08</v>
       </c>
       <c r="R58" t="n">
-        <v>104.5</v>
+        <v>92.3</v>
       </c>
       <c r="S58" t="n">
-        <v>90.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7979,20 +7189,20 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Tulua</t>
+          <t>Andalucia</t>
         </is>
       </c>
       <c r="P59" t="n">
         <v>13.08</v>
       </c>
       <c r="Q59" t="n">
-        <v>55.52</v>
+        <v>43.36</v>
       </c>
       <c r="R59" t="n">
-        <v>104.5</v>
+        <v>92.3</v>
       </c>
       <c r="S59" t="n">
-        <v>90.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8073,74 +7283,84 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SEDE PRINCIPAL LICEO MODERNO</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>176834000106</t>
+          <t>276828000174</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO. 6AW 240</t>
+          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
+          <t>Andalucia</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
           <t>Tulua</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Tulua</t>
-        </is>
-      </c>
       <c r="P60" t="n">
-        <v>7.41</v>
+        <v>90.59</v>
       </c>
       <c r="Q60" t="n">
-        <v>42.09</v>
+        <v>69.08</v>
       </c>
       <c r="R60" t="n">
-        <v>100.2</v>
+        <v>159.7</v>
       </c>
       <c r="S60" t="n">
-        <v>57</v>
+        <v>86.3</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>via principal pavimentada</t>
+          <t>via terciaria</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -8150,12 +7370,12 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
+          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Calle 27</t>
+          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8164,10 +7384,10 @@
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>4.088515899</v>
+        <v>4.210564</v>
       </c>
       <c r="AD60" t="n">
-        <v>-76.22009</v>
+        <v>-76.38158300000001</v>
       </c>
     </row>
     <row r="61">
@@ -8186,48 +7406,48 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>miércoles</t>
+          <t>jueves</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>JOSE MARIA CORDOBA</t>
+          <t>SEDE PRINCIPAL LICEO MODERNO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>276616000212</t>
+          <t>176834000106</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>CORREG SALONICA</t>
+          <t>IND CALLE 27 NO. 6AW 240</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8241,10 +7461,10 @@
         </is>
       </c>
       <c r="P61" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="Q61" t="n">
         <v>42.09</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>50.65</v>
       </c>
       <c r="R61" t="n">
         <v>100.2</v>
@@ -8252,19 +7472,9 @@
       <c r="S61" t="n">
         <v>57</v>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Peligro de colapso</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>en revisión de la mesa</t>
-        </is>
-      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Riesgo inminente de colapso</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8274,7 +7484,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>via principal pavimentada</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8284,12 +7494,12 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es via principal pavimentada según OpenStreetMap (clase «secondary»). La sede queda a 12 m de esa vía.</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
+          <t>Calle 27</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8298,10 +7508,10 @@
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>4.1258314</v>
+        <v>4.088515899</v>
       </c>
       <c r="AD61" t="n">
-        <v>-76.3722336</v>
+        <v>-76.22009</v>
       </c>
     </row>
     <row r="62">
@@ -8327,41 +7537,41 @@
         <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>BID (43)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
+          <t>JOSE MARIA CORDOBA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
+          <t>INSTITUCION EDUCATIVA HERNANDO LLORENTE ARROYO</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>176834000599</t>
+          <t>276616000212</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>IND CALLE 27 NO 6AW 240</t>
+          <t>CORREG SALONICA</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8375,40 +7585,55 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>9.890000000000001</v>
+        <v>42.09</v>
       </c>
       <c r="Q62" t="n">
-        <v>32.44</v>
+        <v>50.65</v>
       </c>
       <c r="R62" t="n">
-        <v>84.09999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="S62" t="n">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Peligro de colapso</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>en revisión de la mesa</t>
+        </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Riesgo inminente de colapso</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>camino destapado</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>SALONICA CRUCE CON VIA 23VL13-1 EN K44+300</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8417,10 +7642,10 @@
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>4.090555556</v>
+        <v>4.1258314</v>
       </c>
       <c r="AD62" t="n">
-        <v>-76.22221999999999</v>
+        <v>-76.3722336</v>
       </c>
     </row>
     <row r="63">
@@ -8439,48 +7664,48 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jueves</t>
+          <t>viernes</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BID (43)</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ALFREDO GARRIDO TOVAR</t>
+          <t>SEDE INSTITUTO CAMPESTRE SANTA CECILIA</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
+          <t>INSTITUCION EDUCATIVA MODERNA DE TULUA</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>276616000654</t>
+          <t>176834000599</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>RIOFRIO</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>CORREG PORTUGAL DE PIEDRAS</t>
+          <t>IND CALLE 27 NO 6AW 240</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8494,10 +7719,10 @@
         </is>
       </c>
       <c r="P63" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="Q63" t="n">
         <v>32.44</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>41.58</v>
       </c>
       <c r="R63" t="n">
         <v>84.09999999999999</v>
@@ -8505,29 +7730,19 @@
       <c r="S63" t="n">
         <v>59</v>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>No habitable</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
-      </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>camino rural sin categoria</t>
+          <t>camino destapado</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -8537,12 +7752,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
+          <t>OpenStreetMap la marca como «track», la clase de los caminos de uso agrícola o forestal. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 50 m de esa vía.</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8551,10 +7761,10 @@
         </is>
       </c>
       <c r="AC63" t="n">
-        <v>4.0553</v>
+        <v>4.090555556</v>
       </c>
       <c r="AD63" t="n">
-        <v>-76.35465000000001</v>
+        <v>-76.22221999999999</v>
       </c>
     </row>
     <row r="64">
@@ -8580,7 +7790,7 @@
         <v>11</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8589,32 +7799,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>INTEGRADA DE TRUJILLO</t>
+          <t>ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
+          <t>INSTITUCION EDUCATIVA ALFREDO GARRIDO TOVAR</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>176828000021</t>
+          <t>276616000654</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>RIOFRIO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Urbana</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>KR 18 15 40</t>
+          <t>CORREG PORTUGAL DE PIEDRAS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8628,16 +7838,16 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>46.98</v>
+        <v>32.44</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.67</v>
+        <v>41.58</v>
       </c>
       <c r="R64" t="n">
-        <v>91.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="S64" t="n">
-        <v>48.5</v>
+        <v>59</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8651,32 +7861,32 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>calle de casco urbano</t>
+          <t>camino rural sin categoria</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
+          <t>OpenStreetMap la marca como «unclassified», una vía menor por debajo de las terciarias. La clase no dice si está pavimentada; conviene confirmar el estado antes de salir. La sede queda a 36 m de esa vía.</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Carrera 18</t>
+          <t>PORTUGAL DE PIEDRAS - CRUCE VIA 23VL13</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8685,10 +7895,10 @@
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>4.208406</v>
+        <v>4.0553</v>
       </c>
       <c r="AD64" t="n">
-        <v>-76.31959500000001</v>
+        <v>-76.35465000000001</v>
       </c>
     </row>
     <row r="65">
@@ -8707,14 +7917,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>viernes</t>
+          <t>sábado</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8723,7 +7933,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8733,7 +7943,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>176828000064</t>
+          <t>176828000021</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8748,7 +7958,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>KR 18 15 27</t>
+          <t>KR 18 15 40</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -8762,10 +7972,10 @@
         </is>
       </c>
       <c r="P65" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="Q65" t="n">
         <v>0.67</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>44.3</v>
       </c>
       <c r="R65" t="n">
         <v>91.90000000000001</v>
@@ -8773,14 +7983,24 @@
       <c r="S65" t="n">
         <v>48.5</v>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>No habitable</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>aprobado por la mesa</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Colapso parcial</t>
+          <t>Afectación parcial</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Critico</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -8795,7 +8015,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 33 m de esa vía.</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8809,10 +8029,10 @@
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>4.210077</v>
+        <v>4.208406</v>
       </c>
       <c r="AD65" t="n">
-        <v>-76.319047</v>
+        <v>-76.31959500000001</v>
       </c>
     </row>
     <row r="66">
@@ -8838,7 +8058,7 @@
         <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8847,17 +8067,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>INSTITUCION EDUCATIVA SAN ISIDRO</t>
+          <t>INSTITUCION EDUCATIVA INTEGRADA DE TRUJILLO</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>276828000174</t>
+          <t>176828000064</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8867,12 +8087,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>CORREGIMIENTO EL TABOR PUENTE BLANCO</t>
+          <t>KR 18 15 27</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -8886,40 +8106,30 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>77.20999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>69.08</v>
+        <v>44.3</v>
       </c>
       <c r="R66" t="n">
-        <v>146.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S66" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Habitable</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>aprobado por la mesa</t>
-        </is>
+        <v>48.5</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Afectación parcial</t>
+          <t>Colapso parcial</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Critico</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>via terciaria</t>
+          <t>calle de casco urbano</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -8929,12 +8139,12 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>La vía de entrada es via terciaria según OpenStreetMap (clase «tertiary»). La sede queda a 33 m de esa vía.</t>
+          <t>La vía de entrada es calle de casco urbano según OpenStreetMap (clase «residential»). La sede queda a 26 m de esa vía.</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>TRUJILLO - LA SONORA CRUCE VIA 23VL13-1 K64+160</t>
+          <t>Carrera 18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -8943,10 +8153,10 @@
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>4.210564</v>
+        <v>4.210077</v>
       </c>
       <c r="AD66" t="n">
-        <v>-76.38158300000001</v>
+        <v>-76.319047</v>
       </c>
     </row>
     <row r="67">
@@ -9658,7 +8868,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
